--- a/Hardware/Hardware Data.xlsx
+++ b/Hardware/Hardware Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\developer\Downloads\CISCO-omrezje-master\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0194A645-EBF2-4DAA-A20D-10E5D1AAB6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A52D85-3C48-4A16-8075-8EC1F70A4A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5338E686-FE58-4924-B8C8-73F6880E9BEF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5338E686-FE58-4924-B8C8-73F6880E9BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,14 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>Produc Name</t>
   </si>
   <si>
-    <t>Serial Number</t>
-  </si>
-  <si>
     <t>Manufacturer</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>HP</t>
   </si>
   <si>
-    <t>C8NZ6AV</t>
-  </si>
-  <si>
     <t>HP desktop PC</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
     <t>In setup</t>
   </si>
   <si>
-    <t>1EX82EA</t>
-  </si>
-  <si>
     <t>HP desktop mini PC</t>
   </si>
   <si>
@@ -210,6 +201,33 @@
   </si>
   <si>
     <t>Lab</t>
+  </si>
+  <si>
+    <t>Serial number</t>
+  </si>
+  <si>
+    <t>Product Number</t>
+  </si>
+  <si>
+    <t>Y5F30AV</t>
+  </si>
+  <si>
+    <t>C8M86AV</t>
+  </si>
+  <si>
+    <t>Z-010</t>
+  </si>
+  <si>
+    <t>8CG7I23VSL</t>
+  </si>
+  <si>
+    <t>CZC34648YR</t>
+  </si>
+  <si>
+    <t>HE208QB0V5Q/302/r2</t>
+  </si>
+  <si>
+    <t>295986-002</t>
   </si>
 </sst>
 </file>
@@ -343,11 +361,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -708,375 +723,428 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F55389-5107-45D0-BDBF-E72D7D4CD374}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="I1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>55</v>
+      <c r="G2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="2">
+        <v>24151</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3">
-        <v>24151</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="K11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
